--- a/artfynd/A 47051-2020 artfynd.xlsx
+++ b/artfynd/A 47051-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47051-2020 artfynd.xlsx
+++ b/artfynd/A 47051-2020 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>119927344</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
